--- a/docs/test-cases/SPM-93_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-93_Test_Cases.xlsx
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Written before the code (TDD, 2026-10-08), then built to them on 2026-10-08: every label, message and page address in the cases is what the code shows (checked against the screens' automated tests, not yet walked through by hand). Checked against the Week 1 briefing, Week 4 instructions, Week 7 Customer Changes and the discussion logs up to 20261006 (#124-#129). Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
+          <t>Written before the code (TDD, 2026-10-09), then built to them on 2026-10-09: every label, message and page address in the cases is what the code shows (checked against the screens' automated tests, not yet walked through by hand). Checked against the Week 1 briefing, Week 4 instructions, Week 7 Customer Changes and the discussion logs up to 20261006 (#124-#129). Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08: the request page (S-15, 'Request a venue booking') replaces the AM/PM/Night checkboxes with 'Date', 'Start time' and 'End time' fields (one date per request, as before). The time fields accept any minute, so an off-grid time reaches the page's own check and its message rather than the browser's. Under them: 'Setup: HH:MM–HH:MM (N min)', 'Turnaround: HH:MM–HH:MM (N min)' and 'Room in use: HH:MM–HH:MM', or 'No setup or turnaround needed at this venue.' and 'Room in use: …' when both are zero.</t>
+          <t>DECIDED 2026-10-09: the request page (S-15, 'Request a venue booking') replaces the AM/PM/Night checkboxes with 'Date', 'Start time' and 'End time' fields (one date per request, as before). The time fields accept any minute, so an off-grid time reaches the page's own check and its message rather than the browser's. Under them: 'Setup: HH:MM–HH:MM (N min)', 'Turnaround: HH:MM–HH:MM (N min)' and 'Room in use: HH:MM–HH:MM', or 'No setup or turnaround needed at this venue.' and 'Room in use: …' when both are zero.</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08: refusal messages (AC3). Shown under the field: 'Choose a start time on a 15-minute step (:00, :15, :30 or :45).', 'Choose an end time on a 15-minute step (:00, :15, :30 or :45).', 'The end time must be after the start time.' The server applies the same checks.</t>
+          <t>DECIDED 2026-10-09: refusal messages (AC3). Shown under the field: 'Choose a start time on a 15-minute step (:00, :15, :30 or :45).', 'Choose an end time on a 15-minute step (:00, :15, :30 or :45).', 'The end time must be after the start time.' The server applies the same checks.</t>
         </is>
       </c>
       <c r="C4" s="11" t="n"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08: the SPM-42 rule that the request must cover the event's (or session's) own time is kept, reworded 'The requested times do not cover the event's time (&lt;date&gt;, &lt;times&gt;).' ('session's' for a session).</t>
+          <t>DECIDED 2026-10-09: the SPM-42 rule that the request must cover the event's (or session's) own time is kept, reworded 'The requested times do not cover the event's time (&lt;date&gt;, &lt;times&gt;).' ('session's' for a session).</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08 (AC4, AC6): the whole room-in-use period, setup and turnaround included, must fit within the venue's opening hours, at request time and in Find a venue. Refusal: '&lt;venue&gt; is open 07:00–22:00. With its &lt;n&gt; min setup and &lt;n&gt; min turnaround, choose times between &lt;earliest start&gt; and &lt;latest end&gt;.' Not stated outright; inferred from Week 1 briefing (venue suitability depends on 'operating hours, setup requirements, and the turnaround time'), Week 7 Change #1 (setup and turnaround are when the venue is 'effectively occupied' and 'must be included when checking availability') and #46 (Venue Staff maintain operating hours). Our own question #131 (Q3, hours a venue can be booked) is still unanswered on 2026-10-08; if the customer rules otherwise, that ruling wins.</t>
+          <t>DECIDED 2026-10-09 (AC4, AC6): the whole room-in-use period, setup and turnaround included, must fit within the venue's opening hours, at request time and in Find a venue. Refusal: '&lt;venue&gt; is open 07:00–22:00. With its &lt;n&gt; min setup and &lt;n&gt; min turnaround, choose times between &lt;earliest start&gt; and &lt;latest end&gt;.' Not stated outright; inferred from Week 1 briefing (venue suitability depends on 'operating hours, setup requirements, and the turnaround time'), Week 7 Change #1 (setup and turnaround are when the venue is 'effectively occupied' and 'must be included when checking availability') and #46 (Venue Staff maintain operating hours). Our own question #131 (Q3, hours a venue can be booked) is still unanswered on 2026-10-09; if the customer rules otherwise, that ruling wins.</t>
         </is>
       </c>
       <c r="C6" s="11" t="n"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09: refusals follow SPM-44 (Detect Venue Booking Conflicts, merged to main 2026-10-08), which names what is in the way (its AC9), with SPM-93's times in place of slots. At request time: '&lt;venue&gt; is already booked for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.' and '&lt;venue&gt; is on hold for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.', where the times are the minutes both need; '&lt;venue&gt; is unavailable at this time (&lt;reason&gt;, &lt;the period's own times&gt;).'; a repeat of the same request: 'This event already has a pending request for &lt;venue&gt; on &lt;date&gt;, &lt;times&gt;.' At approval: 'This overlaps an approved booking: &lt;reference&gt; &lt;title&gt; holds &lt;venue&gt; on &lt;date&gt;, &lt;times&gt; (room in use &lt;times&gt;).' plus ' The clash is through setup or turnaround time.' when the event times themselves do not overlap.</t>
+          <t>DECIDED 2026-10-09: refusals follow SPM-44 (Detect Venue Booking Conflicts, merged to main 2026-10-09), which names what is in the way (its AC9), with SPM-93's times in place of slots. At request time: '&lt;venue&gt; is already booked for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.' and '&lt;venue&gt; is on hold for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.', where the times are the minutes both need; '&lt;venue&gt; is unavailable at this time (&lt;reason&gt;, &lt;the period's own times&gt;).'; a repeat of the same request: 'This event already has a pending request for &lt;venue&gt; on &lt;date&gt;, &lt;times&gt;.' At approval: 'This overlaps an approved booking: &lt;reference&gt; &lt;title&gt; holds &lt;venue&gt; on &lt;date&gt;, &lt;times&gt; (room in use &lt;times&gt;).' plus ' The clash is through setup or turnaround time.' when the event times themselves do not overlap.</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08: on Booking Requests (S-22) the 'Requested' row shows '&lt;date&gt;, &lt;start&gt;–&lt;end&gt;' with the Setup, Turnaround and Room in use lines underneath (AC8). The approve dialog reads 'This books &lt;venue&gt; for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;times&gt;. No other event can then be booked into the room from &lt;start&gt; to &lt;end&gt;, which includes its setup and turnaround time.' The event's Venue tab shows each request as '&lt;date&gt;, &lt;start&gt;–&lt;end&gt; · &lt;layout&gt;'.</t>
+          <t>DECIDED 2026-10-09: on Booking Requests (S-22) the 'Requested' row shows '&lt;date&gt;, &lt;start&gt;–&lt;end&gt;' with the Setup, Turnaround and Room in use lines underneath (AC8). The approve dialog reads 'This books &lt;venue&gt; for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;times&gt;. No other event can then be booked into the room from &lt;start&gt; to &lt;end&gt;, which includes its setup and turnaround time.' The event's Venue tab shows each request as '&lt;date&gt;, &lt;start&gt;–&lt;end&gt; · &lt;layout&gt;'.</t>
         </is>
       </c>
       <c r="C8" s="11" t="n"/>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08: venue form labels become 'Setup time (minutes)' and 'Turnaround time (minutes)' (the customer's word; the database field stays teardownMinutes). Hint 'In 15-minute steps: 0, 15, 30, 45 and so on.' Error 'Enter minutes in 15-minute steps: 0, 15, 30, 45 and so on.' The existing 'Enter a whole number of minutes, 0 or more.' still covers negative and non-numeric values. The calendar subtitle says 'turnaround' instead of 'teardown'. Week 7 Change #1 names only 'setup time' and 'turnaround time'; #43's 'teardown' is the same period.</t>
+          <t>DECIDED 2026-10-09: venue form labels become 'Setup time (minutes)' and 'Turnaround time (minutes)' (the customer's word; the database field stays teardownMinutes). Hint 'In 15-minute steps: 0, 15, 30, 45 and so on.' Error 'Enter minutes in 15-minute steps: 0, 15, 30, 45 and so on.' The existing 'Enter a whole number of minutes, 0 or more.' still covers negative and non-numeric values. The calendar subtitle says 'turnaround' instead of 'teardown'. Week 7 Change #1 names only 'setup time' and 'turnaround time'; #43's 'teardown' is the same period.</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-08 (AC9): the availability calendar (S-21) keeps one row per day but replaces the AM/PM/Night columns with one 'Schedule' column. Each entry reads '&lt;kind&gt; HH:MM–HH:MM · &lt;event title or reason&gt;', in time order, where kind is 'Setup', 'Booked', 'Turnaround', 'Requested' (a pending hold) or 'Unavailable'. An empty day shows 'Free' ('Closed' for a retired venue). The Unavailable periods card shows times, not just dates. The warning about minutes 'outside the AM, PM and Night slots' is removed. Layout is ours to choose: #6 says calendar granularity 'is a UI/UX question, please propose'.</t>
+          <t>DECIDED 2026-10-09 (AC9): the availability calendar (S-21) keeps one row per day but replaces the AM/PM/Night columns with one 'Schedule' column. Each entry reads '&lt;kind&gt; HH:MM–HH:MM · &lt;event title or reason&gt;', in time order, where kind is 'Setup', 'Booked', 'Turnaround', 'Requested' (a pending hold) or 'Unavailable'. An empty day shows 'Free' ('Closed' for a retired venue). The Unavailable periods card shows times, not just dates. The warning about minutes 'outside the AM, PM and Night slots' is removed. Layout is ours to choose: #6 says calendar granularity 'is a UI/UX question, please propose'.</t>
         </is>
       </c>
       <c r="C10" s="11" t="n"/>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10">

--- a/docs/test-cases/SPM-93_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-93_Test_Cases.xlsx
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Written before the code (TDD, 2026-10-09), then built to them on 2026-10-09: every label, message and page address in the cases is what the code shows (checked against the screens' automated tests, not yet walked through by hand). Checked against the Week 1 briefing, Week 4 instructions, Week 7 Customer Changes and the discussion logs up to 20261006 (#124-#129). Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
+          <t>Written before the code (TDD, 2026-10-08), then built to them on 2026-10-08: every label, message and page address in the cases is what the code shows (checked against the screens' automated tests, not yet walked through by hand). Checked against the Week 1 briefing, Week 4 instructions, Week 7 Customer Changes and the discussion logs up to 20261006 (#124-#129). Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09: the request page (S-15, 'Request a venue booking') replaces the AM/PM/Night checkboxes with 'Date', 'Start time' and 'End time' fields (one date per request, as before). The time fields accept any minute, so an off-grid time reaches the page's own check and its message rather than the browser's. Under them: 'Setup: HH:MM–HH:MM (N min)', 'Turnaround: HH:MM–HH:MM (N min)' and 'Room in use: HH:MM–HH:MM', or 'No setup or turnaround needed at this venue.' and 'Room in use: …' when both are zero.</t>
+          <t>DECIDED 2026-10-08: the request page (S-15, 'Request a venue booking') replaces the AM/PM/Night checkboxes with 'Date', 'Start time' and 'End time' fields (one date per request, as before). The time fields accept any minute, so an off-grid time reaches the page's own check and its message rather than the browser's. Under them: 'Setup: HH:MM–HH:MM (N min)', 'Turnaround: HH:MM–HH:MM (N min)' and 'Room in use: HH:MM–HH:MM', or 'No setup or turnaround needed at this venue.' and 'Room in use: …' when both are zero.</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09: refusal messages (AC3). Shown under the field: 'Choose a start time on a 15-minute step (:00, :15, :30 or :45).', 'Choose an end time on a 15-minute step (:00, :15, :30 or :45).', 'The end time must be after the start time.' The server applies the same checks.</t>
+          <t>DECIDED 2026-10-08: refusal messages (AC3). Shown under the field: 'Choose a start time on a 15-minute step (:00, :15, :30 or :45).', 'Choose an end time on a 15-minute step (:00, :15, :30 or :45).', 'The end time must be after the start time.' The server applies the same checks.</t>
         </is>
       </c>
       <c r="C4" s="11" t="n"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09: the SPM-42 rule that the request must cover the event's (or session's) own time is kept, reworded 'The requested times do not cover the event's time (&lt;date&gt;, &lt;times&gt;).' ('session's' for a session).</t>
+          <t>DECIDED 2026-10-08: the SPM-42 rule that the request must cover the event's (or session's) own time is kept, reworded 'The requested times do not cover the event's time (&lt;date&gt;, &lt;times&gt;).' ('session's' for a session).</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09 (AC4, AC6): the whole room-in-use period, setup and turnaround included, must fit within the venue's opening hours, at request time and in Find a venue. Refusal: '&lt;venue&gt; is open 07:00–22:00. With its &lt;n&gt; min setup and &lt;n&gt; min turnaround, choose times between &lt;earliest start&gt; and &lt;latest end&gt;.' Not stated outright; inferred from Week 1 briefing (venue suitability depends on 'operating hours, setup requirements, and the turnaround time'), Week 7 Change #1 (setup and turnaround are when the venue is 'effectively occupied' and 'must be included when checking availability') and #46 (Venue Staff maintain operating hours). Our own question #131 (Q3, hours a venue can be booked) is still unanswered on 2026-10-09; if the customer rules otherwise, that ruling wins.</t>
+          <t>DECIDED 2026-10-08 (AC4, AC6): the whole room-in-use period, setup and turnaround included, must fit within the venue's opening hours, at request time and in Find a venue. Refusal: '&lt;venue&gt; is open 07:00–22:00. With its &lt;n&gt; min setup and &lt;n&gt; min turnaround, choose times between &lt;earliest start&gt; and &lt;latest end&gt;.' Not stated outright; inferred from Week 1 briefing (venue suitability depends on 'operating hours, setup requirements, and the turnaround time'), Week 7 Change #1 (setup and turnaround are when the venue is 'effectively occupied' and 'must be included when checking availability') and #46 (Venue Staff maintain operating hours). Our own question #131 (Q3, hours a venue can be booked) is still unanswered on 2026-10-08; if the customer rules otherwise, that ruling wins.</t>
         </is>
       </c>
       <c r="C6" s="11" t="n"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09: refusals follow SPM-44 (Detect Venue Booking Conflicts, merged to main 2026-10-09), which names what is in the way (its AC9), with SPM-93's times in place of slots. At request time: '&lt;venue&gt; is already booked for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.' and '&lt;venue&gt; is on hold for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.', where the times are the minutes both need; '&lt;venue&gt; is unavailable at this time (&lt;reason&gt;, &lt;the period's own times&gt;).'; a repeat of the same request: 'This event already has a pending request for &lt;venue&gt; on &lt;date&gt;, &lt;times&gt;.' At approval: 'This overlaps an approved booking: &lt;reference&gt; &lt;title&gt; holds &lt;venue&gt; on &lt;date&gt;, &lt;times&gt; (room in use &lt;times&gt;).' plus ' The clash is through setup or turnaround time.' when the event times themselves do not overlap.</t>
+          <t>DECIDED 2026-10-08: refusals follow SPM-44 (Detect Venue Booking Conflicts, merged to main 2026-10-08), which names what is in the way (its AC9), with SPM-93's times in place of slots. At request time: '&lt;venue&gt; is already booked for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.' and '&lt;venue&gt; is on hold for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.', where the times are the minutes both need; '&lt;venue&gt; is unavailable at this time (&lt;reason&gt;, &lt;the period's own times&gt;).'; a repeat of the same request: 'This event already has a pending request for &lt;venue&gt; on &lt;date&gt;, &lt;times&gt;.' At approval: 'This overlaps an approved booking: &lt;reference&gt; &lt;title&gt; holds &lt;venue&gt; on &lt;date&gt;, &lt;times&gt; (room in use &lt;times&gt;).' plus ' The clash is through setup or turnaround time.' when the event times themselves do not overlap.</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09: on Booking Requests (S-22) the 'Requested' row shows '&lt;date&gt;, &lt;start&gt;–&lt;end&gt;' with the Setup, Turnaround and Room in use lines underneath (AC8). The approve dialog reads 'This books &lt;venue&gt; for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;times&gt;. No other event can then be booked into the room from &lt;start&gt; to &lt;end&gt;, which includes its setup and turnaround time.' The event's Venue tab shows each request as '&lt;date&gt;, &lt;start&gt;–&lt;end&gt; · &lt;layout&gt;'.</t>
+          <t>DECIDED 2026-10-08: on Booking Requests (S-22) the 'Requested' row shows '&lt;date&gt;, &lt;start&gt;–&lt;end&gt;' with the Setup, Turnaround and Room in use lines underneath (AC8). The approve dialog reads 'This books &lt;venue&gt; for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;times&gt;. No other event can then be booked into the room from &lt;start&gt; to &lt;end&gt;, which includes its setup and turnaround time.' The event's Venue tab shows each request as '&lt;date&gt;, &lt;start&gt;–&lt;end&gt; · &lt;layout&gt;'.</t>
         </is>
       </c>
       <c r="C8" s="11" t="n"/>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09: venue form labels become 'Setup time (minutes)' and 'Turnaround time (minutes)' (the customer's word; the database field stays teardownMinutes). Hint 'In 15-minute steps: 0, 15, 30, 45 and so on.' Error 'Enter minutes in 15-minute steps: 0, 15, 30, 45 and so on.' The existing 'Enter a whole number of minutes, 0 or more.' still covers negative and non-numeric values. The calendar subtitle says 'turnaround' instead of 'teardown'. Week 7 Change #1 names only 'setup time' and 'turnaround time'; #43's 'teardown' is the same period.</t>
+          <t>DECIDED 2026-10-08: venue form labels become 'Setup time (minutes)' and 'Turnaround time (minutes)' (the customer's word; the database field stays teardownMinutes). Hint 'In 15-minute steps: 0, 15, 30, 45 and so on.' Error 'Enter minutes in 15-minute steps: 0, 15, 30, 45 and so on.' The existing 'Enter a whole number of minutes, 0 or more.' still covers negative and non-numeric values. The calendar subtitle says 'turnaround' instead of 'teardown'. Week 7 Change #1 names only 'setup time' and 'turnaround time'; #43's 'teardown' is the same period.</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>DECIDED 2026-10-09 (AC9): the availability calendar (S-21) keeps one row per day but replaces the AM/PM/Night columns with one 'Schedule' column. Each entry reads '&lt;kind&gt; HH:MM–HH:MM · &lt;event title or reason&gt;', in time order, where kind is 'Setup', 'Booked', 'Turnaround', 'Requested' (a pending hold) or 'Unavailable'. An empty day shows 'Free' ('Closed' for a retired venue). The Unavailable periods card shows times, not just dates. The warning about minutes 'outside the AM, PM and Night slots' is removed. Layout is ours to choose: #6 says calendar granularity 'is a UI/UX question, please propose'.</t>
+          <t>DECIDED 2026-10-08 (AC9): the availability calendar (S-21) keeps one row per day but replaces the AM/PM/Night columns with one 'Schedule' column. Each entry reads '&lt;kind&gt; HH:MM–HH:MM · &lt;event title or reason&gt;', in time order, where kind is 'Setup', 'Booked', 'Turnaround', 'Requested' (a pending hold) or 'Unavailable'. An empty day shows 'Free' ('Closed' for a retired venue). The Unavailable periods card shows times, not just dates. The warning about minutes 'outside the AM, PM and Night slots' is removed. Layout is ours to choose: #6 says calendar granularity 'is a UI/UX question, please propose'.</t>
         </is>
       </c>
       <c r="C10" s="11" t="n"/>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10">

--- a/docs/test-cases/SPM-93_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-93_Test_Cases.xlsx
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Written before the code (TDD, 2026-10-08), then built to them on 2026-10-08: every label, message and page address in the cases is what the code shows (checked against the screens' automated tests, not yet walked through by hand). Checked against the Week 1 briefing, Week 4 instructions, Week 7 Customer Changes and the discussion logs up to 20261006 (#124-#129). Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
+          <t>Written before the code (TDD, 2026-10-08), then built to them on 2026-10-08: every label, message and page address in the cases is what the code shows, and all 17 cases passed when run by hand. Checked against the Week 1 briefing, Week 4 instructions, Week 7 Customer Changes and the discussion logs up to 20261006 (#124-#129). Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>

--- a/docs/test-cases/SPM-93_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-93_Test_Cases.xlsx
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -189,6 +189,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -481,12 +484,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="19">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>SPM-93: As an Event Coordinator, I want to book a venue for the times my event needs, in 15-minute steps, so that a venue is not held for a whole morning, afternoon or night when the event needs only part of it</t>
         </is>
@@ -498,32 +501,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -550,27 +553,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC01</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>A request defaults to the event's times widened to the 15-minute grid, shows the setup and turnaround around them, and is sent as times, not slots</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>AC1, AC2, AC6</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -589,27 +592,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC02</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>For a multi-session event the request defaults to the chosen session's own times, widened only where they are off the grid</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -628,27 +631,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC03</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Times off the 15-minute grid, and an end that is not after the start, are refused and the wrong time is named</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>AC3, AC1</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -667,27 +670,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC04</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Requested times that do not cover the event's own time are refused</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>AC1, AC2</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -706,27 +709,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC05</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>The old lunch and dinner gaps (12:00–13:00 and 18:00–19:00) can be booked</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>AC4, AC1</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -745,27 +748,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC06</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>The room in use, setup and turnaround included, must fit within opening hours; times that just fit are accepted, a quarter-hour more is refused</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>AC4, AC6</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -784,38 +787,42 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC07</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Venue Staff set setup and turnaround time in 15-minute steps, including zero; other minute values are refused</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H10" s="23" t="n"/>
-      <c r="I10" s="23" t="n"/>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>Week 7 #1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -823,27 +830,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC08</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>At a venue with no setup or turnaround, the room is in use only for the booked times, so a booking can start the minute another ends</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>AC5, AC6, AC7</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -862,27 +869,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC09</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>A request whose turnaround runs into an approved booking's setup is refused; one whose turnaround ends as that setup starts is accepted</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>AC6, AC7</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -901,27 +908,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC10</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>A request whose setup runs into an approved booking's turnaround is refused; one whose setup starts as that turnaround ends is accepted</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>AC6, AC7</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -940,27 +947,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC11</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>A pending request (tentative hold) also holds the room for its setup and turnaround</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>AC6, AC7</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -979,27 +986,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC12</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>A request whose setup would run into an unavailable period is refused; one whose setup starts as the period ends is accepted</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>AC6, AC7</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1018,27 +1025,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC13</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>Venue Staff see a request's times and the room in use including setup and turnaround, on the card and in the approve dialog</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1057,27 +1064,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC14</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>After one request is approved, a request whose setup overlaps its turnaround is in conflict, and one that only meets it can still be approved</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>AC7, AC8, AC6</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1096,27 +1103,27 @@
           <t>TC15</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC15</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>The availability calendar shows an approved booking and a pending hold at their actual times, with setup and turnaround as separate entries</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>AC9</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1135,27 +1142,27 @@
           <t>TC16</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC16</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>The calendar shows a part-day unavailable period at its times, and no setup or turnaround entries for a venue that needs none</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>AC9, AC5</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1174,27 +1181,27 @@
           <t>TC17</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC17</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Find a venue leaves out a venue whose setup or turnaround would overlap an approved booking, and offers it when the times only meet</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>AC6, AC7</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1210,19 +1217,19 @@
     <row r="21" ht="15.75" customHeight="1" s="19"/>
     <row r="22" ht="15.75" customHeight="1" s="19"/>
     <row r="23" ht="15.75" customHeight="1" s="19">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C23" s="20" t="n"/>
       <c r="D23" s="21" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1230,19 +1237,19 @@
       <c r="F23" s="21" t="n"/>
     </row>
     <row r="24" ht="57.75" customHeight="1" s="19">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A venue booking request is made for a start time and an end time on a 15-minute grid (e.g. 10:00–12:15), not by choosing AM, PM or Night slots.</t>
         </is>
       </c>
       <c r="C24" s="20" t="n"/>
       <c r="D24" s="21" t="n"/>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC01
 SPM-93-TC03
@@ -1253,19 +1260,19 @@
       <c r="F24" s="21" t="n"/>
     </row>
     <row r="25" ht="44.25" customHeight="1" s="19">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>The requested times default to the event's (or the session's) own start and end, widened to the nearest 15 minutes where they do not fall on the grid.</t>
         </is>
       </c>
       <c r="C25" s="20" t="n"/>
       <c r="D25" s="21" t="n"/>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC01
 SPM-93-TC02
@@ -1275,19 +1282,19 @@
       <c r="F25" s="21" t="n"/>
     </row>
     <row r="26" ht="44.25" customHeight="1" s="19">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>Given a start or end time is not on a 15-minute boundary, or the end is not after the start, when the request is submitted, then it is refused and the time is identified.</t>
         </is>
       </c>
       <c r="C26" s="20" t="n"/>
       <c r="D26" s="21" t="n"/>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC03</t>
         </is>
@@ -1295,19 +1302,19 @@
       <c r="F26" s="21" t="n"/>
     </row>
     <row r="27" ht="30.75" customHeight="1" s="19">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>Any period within the venue's opening hours can be booked; there is no fixed lunch or dinner blackout.</t>
         </is>
       </c>
       <c r="C27" s="20" t="n"/>
       <c r="D27" s="21" t="n"/>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC05
 SPM-93-TC06</t>
@@ -1316,19 +1323,19 @@
       <c r="F27" s="21" t="n"/>
     </row>
     <row r="28" ht="44.25" customHeight="1" s="19">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Each venue's setup time and turnaround time are set in minutes, in 15-minute steps (including zero), instead of whole adjacent slots.</t>
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
       <c r="D28" s="21" t="n"/>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC07
 SPM-93-TC08
@@ -1338,19 +1345,19 @@
       <c r="F28" s="21" t="n"/>
     </row>
     <row r="29" ht="125.25" customHeight="1" s="19">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>When availability and conflicts are checked, a booking occupies the venue from its start minus the venue's setup time to its end plus the venue's turnaround time.</t>
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
       <c r="D29" s="21" t="n"/>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC01
 SPM-93-TC06
@@ -1366,19 +1373,19 @@
       <c r="F29" s="21" t="n"/>
     </row>
     <row r="30" ht="98.25" customHeight="1" s="19">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>Two bookings at the same venue conflict when their occupied periods overlap; occupied periods that only meet end to start do not conflict.</t>
         </is>
       </c>
       <c r="C30" s="20" t="n"/>
       <c r="D30" s="21" t="n"/>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC08
 SPM-93-TC09
@@ -1392,19 +1399,19 @@
       <c r="F30" s="21" t="n"/>
     </row>
     <row r="31" ht="30.75" customHeight="1" s="19">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>Venue Staff reviewing a request see the requested times and the occupied period including setup and turnaround.</t>
         </is>
       </c>
       <c r="C31" s="20" t="n"/>
       <c r="D31" s="21" t="n"/>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC13
 SPM-93-TC14</t>
@@ -1413,19 +1420,19 @@
       <c r="F31" s="21" t="n"/>
     </row>
     <row r="32" ht="44.25" customHeight="1" s="19">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>AC9</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>The venue availability calendar shows bookings, holds and unavailable periods at their actual times, with setup and turnaround shown separately from the booked time.</t>
         </is>
       </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="21" t="n"/>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC15
 SPM-93-TC16</t>
@@ -1435,12 +1442,12 @@
     </row>
     <row r="33" ht="15.75" customHeight="1" s="19"/>
     <row r="34" ht="233.25" customHeight="1" s="19">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>src/lib/venueTime.ts
 src/lib/venueBookingRequest.ts
@@ -2509,7 +2516,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC08</t>
         </is>
@@ -2521,7 +2528,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` before this case, and again after it: the case sends a booking request.
 'SPM93 Quick Demo' holds an Approved booking at SPM93 Quick Room on 8 Jun 2027, 10:00–12:00.
@@ -2535,7 +2542,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Follow-on Session'
 2. Click the 'Venue' tab
@@ -2550,7 +2557,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Venue: SPM93 Quick Room (SPM93-QCK) | Setup 0 min | Turnaround 0 min
 Approved: SPM93 Quick Demo, 8 Jun 2027, 10:00–12:00
@@ -2564,7 +2571,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 12:00 and 'End time' 13:00. Instead of setup and turnaround lines the page reads 'No setup or turnaround needed at this venue.' and 'Room in use: 12:00–13:00'.
 Step 4: A green alert 'Booking request sent to Venue Staff.' is shown: the room in use ends at 12:00 for SPM93 Quick Demo and starts at 12:00 for this request.</t>
@@ -2577,7 +2584,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -2609,7 +2616,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 12:00 and 'End time' 13:00. Instead of setup and turnaround lines the page reads 'No setup or turnaround needed at this venue.' and 'Room in use: 12:00–13:00'.
 Step 4: A green alert 'Booking request sent to Venue Staff.' is shown: the room in use ends at 12:00 for SPM93 Quick Demo and starts at 12:00 for this request.</t>
@@ -2677,7 +2684,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 12:00 and 'End time' 13:00. Instead of setup and turnaround lines the page reads 'No setup or turnaround needed at this venue.' and 'Room in use: 12:00–13:00'.
 Step 4: A green alert 'Booking request sent to Venue Staff.' is shown: the room in use ends at 12:00 for SPM93 Quick Demo and starts at 12:00 for this request.</t>
@@ -3742,7 +3749,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC09</t>
         </is>
@@ -3754,7 +3761,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` before this case, and again after it: the case sends a booking request.
 'SPM93 Morning Masterclass' holds an Approved booking at SPM93 Studio on 8 Jun 2027, 10:00–12:00, so the room is in use 09:30–12:45.
@@ -3768,7 +3775,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Early Huddle'
 2. Click the 'Venue' tab
@@ -3784,7 +3791,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Venue: SPM93 Studio (SPM93-STU) | Setup 30 min | Turnaround 45 min
 Approved: SPM93 Morning Masterclass, 8 Jun 2027, 10:00–12:00 (room in use 09:30–12:45)
@@ -3799,7 +3806,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 08:15, 'End time' 08:45 and 'Room in use: 07:45–09:30'.
 Step 4: 'Room in use: 07:45–09:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is already booked for &lt;reference&gt; SPM93 Morning Masterclass on 8 Jun 2027, 09:30–09:45.' (the event times never meet the Masterclass's 10:00–12:00; only the turnaround reaches its setup, for those 15 minutes).
@@ -3813,7 +3820,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -3845,7 +3852,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 08:15, 'End time' 08:45 and 'Room in use: 07:45–09:30'.
 Step 4: 'Room in use: 07:45–09:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is already booked for &lt;reference&gt; SPM93 Morning Masterclass on 8 Jun 2027, 09:30–09:45.' (the event times never meet the Masterclass's 10:00–12:00; only the turnaround reaches its setup, for those 15 minutes).
@@ -3914,7 +3921,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 08:15, 'End time' 08:45 and 'Room in use: 07:45–09:30'.
 Step 4: 'Room in use: 07:45–09:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is already booked for &lt;reference&gt; SPM93 Morning Masterclass on 8 Jun 2027, 09:30–09:45.' (the event times never meet the Masterclass's 10:00–12:00; only the turnaround reaches its setup, for those 15 minutes).
@@ -4980,7 +4987,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC10</t>
         </is>
@@ -4992,7 +4999,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` before this case, and again after it: the case sends a booking request.
 'SPM93 Morning Masterclass' holds an Approved booking at SPM93 Studio on 8 Jun 2027, 10:00–12:00, so the room is in use 09:30–12:45.
@@ -5006,7 +5013,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Afternoon Review'
 2. Click the 'Venue' tab
@@ -5022,7 +5029,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Venue: SPM93 Studio (SPM93-STU) | Setup 30 min | Turnaround 45 min
 Approved: SPM93 Morning Masterclass, 8 Jun 2027, 10:00–12:00 (room in use 09:30–12:45)
@@ -5037,7 +5044,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 13:15, 'End time' 14:00 and 'Room in use: 12:45–14:45'.
 Step 4: 'Room in use: 12:30–14:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is already booked for &lt;reference&gt; SPM93 Morning Masterclass on 8 Jun 2027, 12:30–12:45.'
@@ -5051,7 +5058,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -5083,7 +5090,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 13:15, 'End time' 14:00 and 'Room in use: 12:45–14:45'.
 Step 4: 'Room in use: 12:30–14:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is already booked for &lt;reference&gt; SPM93 Morning Masterclass on 8 Jun 2027, 12:30–12:45.'
@@ -5152,7 +5159,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 13:15, 'End time' 14:00 and 'Room in use: 12:45–14:45'.
 Step 4: 'Room in use: 12:30–14:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is already booked for &lt;reference&gt; SPM93 Morning Masterclass on 8 Jun 2027, 12:30–12:45.'
@@ -6218,7 +6225,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC11</t>
         </is>
@@ -6230,7 +6237,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` before this case, and again after it: the case sends a booking request.
 'SPM93 Partner Lunch' has a Pending booking request at SPM93 Studio on 10 Jun 2027, 12:00–13:00, so the room is held 11:30–13:45.
@@ -6244,7 +6251,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Team Sync'
 2. Click the 'Venue' tab
@@ -6260,7 +6267,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Venue: SPM93 Studio (SPM93-STU) | Setup 30 min | Turnaround 45 min
 Pending: SPM93 Partner Lunch, 10 Jun 2027, 12:00–13:00 (held 11:30–13:45)
@@ -6275,7 +6282,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: The request is not sent. A red alert reads 'SPM93 Studio is on hold for &lt;reference&gt; SPM93 Partner Lunch on 10 Jun 2027, 13:30–13:45.'
 Step 5: A green alert 'Booking request sent to Venue Staff.' is shown: the setup starts at 13:45, exactly when the Partner Lunch's turnaround ends.</t>
@@ -6288,7 +6295,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -6320,7 +6327,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: The request is not sent. A red alert reads 'SPM93 Studio is on hold for &lt;reference&gt; SPM93 Partner Lunch on 10 Jun 2027, 13:30–13:45.'
 Step 5: A green alert 'Booking request sent to Venue Staff.' is shown: the setup starts at 13:45, exactly when the Partner Lunch's turnaround ends.</t>
@@ -6388,7 +6395,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: The request is not sent. A red alert reads 'SPM93 Studio is on hold for &lt;reference&gt; SPM93 Partner Lunch on 10 Jun 2027, 13:30–13:45.'
 Step 5: A green alert 'Booking request sent to Venue Staff.' is shown: the setup starts at 13:45, exactly when the Partner Lunch's turnaround ends.</t>
@@ -7453,7 +7460,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC12</t>
         </is>
@@ -7465,7 +7472,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` before this case, and again after it: the case sends a booking request.
 SPM93 Studio is unavailable for maintenance on 16 Jun 2027, 14:00–18:00.
@@ -7479,7 +7486,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Twilight Workshop'
 2. Click the 'Venue' tab
@@ -7495,7 +7502,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Venue: SPM93 Studio (SPM93-STU) | Setup 30 min | Turnaround 45 min
 Unavailable: 16 Jun 2027, 14:00–18:00 (maintenance)
@@ -7510,7 +7517,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 18:30, 'End time' 20:00 and 'Room in use: 18:00–20:45'.
 Step 4: 'Room in use: 17:45–20:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is unavailable at this time (maintenance, 16 Jun 2027, 14:00–18:00).' (the event times are after the maintenance, only the setup reaches into it).
@@ -7524,7 +7531,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -7556,7 +7563,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 18:30, 'End time' 20:00 and 'Room in use: 18:00–20:45'.
 Step 4: 'Room in use: 17:45–20:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is unavailable at this time (maintenance, 16 Jun 2027, 14:00–18:00).' (the event times are after the maintenance, only the setup reaches into it).
@@ -7625,7 +7632,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Start time' shows 18:30, 'End time' 20:00 and 'Room in use: 18:00–20:45'.
 Step 4: 'Room in use: 17:45–20:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is unavailable at this time (maintenance, 16 Jun 2027, 14:00–18:00).' (the event times are after the maintenance, only the setup reaches into it).
@@ -8691,7 +8698,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC13</t>
         </is>
@@ -8703,7 +8710,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>`npm run fixtures:spm93` has been run since the last full `npx prisma db seed`.
 'SPM93 Partner Lunch' has a Pending booking request at SPM93 Studio on 10 Jun 2027, 12:00–13:00.
@@ -8718,7 +8725,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Booking Requests' in the sidebar
 2. Find the 'SPM93 Studio' card for 'SPM93 Partner Lunch' (use Ctrl+F) and click 'Approve'
@@ -8732,7 +8739,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Request: SPM93 Partner Lunch at SPM93 Studio (SPM93-STU), 10 Jun 2027, 12:00–13:00
 Venue: setup 30 min, turnaround 45 min</t>
@@ -8745,7 +8752,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 1: The 'Booking Requests' page lists a card 'SPM93 Studio (SPM93-STU)' for 'SPM93 Partner Lunch' with the 'Pending' badge. Its 'Requested' row reads '10 Jun 2027, 12:00–13:00' and under it 'Setup: 11:30–12:00 (30 min)', 'Turnaround: 13:00–13:45 (45 min)' and 'Room in use: 11:30–13:45'. Nothing on the card mentions AM, PM or Night.
 Step 2: The 'Approve this booking?' dialog reads 'This books SPM93 Studio (SPM93-STU) for &lt;reference&gt; SPM93 Partner Lunch on 10 Jun 2027, 12:00–13:00. No other event can then be booked into the room from 11:30 to 13:45, which includes its setup and turnaround time.'
@@ -8759,7 +8766,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -8791,7 +8798,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 1: The 'Booking Requests' page lists a card 'SPM93 Studio (SPM93-STU)' for 'SPM93 Partner Lunch' with the 'Pending' badge. Its 'Requested' row reads '10 Jun 2027, 12:00–13:00' and under it 'Setup: 11:30–12:00 (30 min)', 'Turnaround: 13:00–13:45 (45 min)' and 'Room in use: 11:30–13:45'. Nothing on the card mentions AM, PM or Night.
 Step 2: The 'Approve this booking?' dialog reads 'This books SPM93 Studio (SPM93-STU) for &lt;reference&gt; SPM93 Partner Lunch on 10 Jun 2027, 12:00–13:00. No other event can then be booked into the room from 11:30 to 13:45, which includes its setup and turnaround time.'
@@ -8860,7 +8867,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 1: The 'Booking Requests' page lists a card 'SPM93 Studio (SPM93-STU)' for 'SPM93 Partner Lunch' with the 'Pending' badge. Its 'Requested' row reads '10 Jun 2027, 12:00–13:00' and under it 'Setup: 11:30–12:00 (30 min)', 'Turnaround: 13:00–13:45 (45 min)' and 'Room in use: 11:30–13:45'. Nothing on the card mentions AM, PM or Night.
 Step 2: The 'Approve this booking?' dialog reads 'This books SPM93 Studio (SPM93-STU) for &lt;reference&gt; SPM93 Partner Lunch on 10 Jun 2027, 12:00–13:00. No other event can then be booked into the room from 11:30 to 13:45, which includes its setup and turnaround time.'
@@ -9926,7 +9933,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC14</t>
         </is>
@@ -9938,7 +9945,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` before this case, and again after it: the case approves two booking requests.
 Three Pending requests at SPM93 Studio on 15 Jun 2027: 'SPM93 Supplier Day' 10:00–12:00, 'SPM93 Vendor Q&amp;A' 13:00–14:00 and 'SPM93 Buyer Briefing' 13:15–14:00. None shows 'Conflict' yet.
@@ -9952,7 +9959,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Booking Requests' in the sidebar
 2. Find the 'SPM93 Studio' card for 'SPM93 Supplier Day' (use Ctrl+F) and click 'Approve'
@@ -9969,7 +9976,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Venue: SPM93 Studio (SPM93-STU) | Setup 30 min | Turnaround 45 min
 SPM93 Supplier Day 10:00–12:00 (room in use 09:30–12:45)
@@ -9984,7 +9991,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: A green alert 'Booking approved' reads 'SPM93 Studio (SPM93-STU) for &lt;reference&gt; SPM93 Supplier Day on 15 Jun 2027, 10:00–12:00 is now Approved — the room is booked.' The Supplier Day card leaves the list.
 Step 4: The Vendor Q&amp;A card shows a red 'Conflict' badge and the alert 'This request cannot be approved as it stands' with 'This overlaps an approved booking: &lt;reference&gt; SPM93 Supplier Day holds SPM93 Studio on 15 Jun 2027, 10:00–12:00 (room in use 09:30–12:45). The clash is through setup or turnaround time.' and an 'Open the calendar' link. Its 'Approve' button is disabled.
@@ -9999,7 +10006,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -10031,7 +10038,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: A green alert 'Booking approved' reads 'SPM93 Studio (SPM93-STU) for &lt;reference&gt; SPM93 Supplier Day on 15 Jun 2027, 10:00–12:00 is now Approved — the room is booked.' The Supplier Day card leaves the list.
 Step 4: The Vendor Q&amp;A card shows a red 'Conflict' badge and the alert 'This request cannot be approved as it stands' with 'This overlaps an approved booking: &lt;reference&gt; SPM93 Supplier Day holds SPM93 Studio on 15 Jun 2027, 10:00–12:00 (room in use 09:30–12:45). The clash is through setup or turnaround time.' and an 'Open the calendar' link. Its 'Approve' button is disabled.
@@ -10101,7 +10108,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: A green alert 'Booking approved' reads 'SPM93 Studio (SPM93-STU) for &lt;reference&gt; SPM93 Supplier Day on 15 Jun 2027, 10:00–12:00 is now Approved — the room is booked.' The Supplier Day card leaves the list.
 Step 4: The Vendor Q&amp;A card shows a red 'Conflict' badge and the alert 'This request cannot be approved as it stands' with 'This overlaps an approved booking: &lt;reference&gt; SPM93 Supplier Day holds SPM93 Studio on 15 Jun 2027, 10:00–12:00 (room in use 09:30–12:45). The clash is through setup or turnaround time.' and an 'Open the calendar' link. Its 'Approve' button is disabled.
@@ -11168,7 +11175,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC15</t>
         </is>
@@ -11180,7 +11187,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>`npm run fixtures:spm93` has been run since the last full `npx prisma db seed`, and no booking request has been sent for an 'SPM93 …' event since.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -11194,7 +11201,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. On the 'SPM93 Studio' row, click 'View availability'
@@ -11208,7 +11215,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Venue: SPM93 Studio (SPM93-STU) | Open 07:00–22:00 | Setup 30 min | Turnaround 45 min
 Approved: SPM93 Morning Masterclass, 8 Jun 2027, 10:00–12:00
@@ -11222,7 +11229,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 2: The 'SPM93 Studio availability' page opens. The grid has two columns, 'Day' and 'Schedule'; there are no AM, PM or Night columns.
 Step 3: The subtitle reads '8 Jun 2027 – 10 Jun 2027 · open 07:00–22:00 · setup 30 min, turnaround 45 min'. Three day rows. 'Tue 8 Jun 2027' lists, in this order, 'Setup 09:30–10:00 · SPM93 Morning Masterclass', 'Booked 10:00–12:00 · SPM93 Morning Masterclass' and 'Turnaround 12:00–12:45 · SPM93 Morning Masterclass'. 'Wed 9 Jun 2027' shows 'Free'. 'Thu 10 Jun 2027' lists 'Setup 11:30–12:00 · SPM93 Partner Lunch', 'Requested 12:00–13:00 · SPM93 Partner Lunch' and 'Turnaround 13:00–13:45 · SPM93 Partner Lunch'. The 'Approved bookings' card lists SPM93 Morning Masterclass with '8 Jun 2027, 10:00–12:00' and 'Room in use 09:30–12:45'. The 'Requested, not yet approved' card lists SPM93 Partner Lunch with '10 Jun 2027, 12:00–13:00'. Nothing on the page mentions AM, PM or Night slots.</t>
@@ -11235,7 +11242,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -11267,7 +11274,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 2: The 'SPM93 Studio availability' page opens. The grid has two columns, 'Day' and 'Schedule'; there are no AM, PM or Night columns.
 Step 3: The subtitle reads '8 Jun 2027 – 10 Jun 2027 · open 07:00–22:00 · setup 30 min, turnaround 45 min'. Three day rows. 'Tue 8 Jun 2027' lists, in this order, 'Setup 09:30–10:00 · SPM93 Morning Masterclass', 'Booked 10:00–12:00 · SPM93 Morning Masterclass' and 'Turnaround 12:00–12:45 · SPM93 Morning Masterclass'. 'Wed 9 Jun 2027' shows 'Free'. 'Thu 10 Jun 2027' lists 'Setup 11:30–12:00 · SPM93 Partner Lunch', 'Requested 12:00–13:00 · SPM93 Partner Lunch' and 'Turnaround 13:00–13:45 · SPM93 Partner Lunch'. The 'Approved bookings' card lists SPM93 Morning Masterclass with '8 Jun 2027, 10:00–12:00' and 'Room in use 09:30–12:45'. The 'Requested, not yet approved' card lists SPM93 Partner Lunch with '10 Jun 2027, 12:00–13:00'. Nothing on the page mentions AM, PM or Night slots.</t>
@@ -11335,7 +11342,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 2: The 'SPM93 Studio availability' page opens. The grid has two columns, 'Day' and 'Schedule'; there are no AM, PM or Night columns.
 Step 3: The subtitle reads '8 Jun 2027 – 10 Jun 2027 · open 07:00–22:00 · setup 30 min, turnaround 45 min'. Three day rows. 'Tue 8 Jun 2027' lists, in this order, 'Setup 09:30–10:00 · SPM93 Morning Masterclass', 'Booked 10:00–12:00 · SPM93 Morning Masterclass' and 'Turnaround 12:00–12:45 · SPM93 Morning Masterclass'. 'Wed 9 Jun 2027' shows 'Free'. 'Thu 10 Jun 2027' lists 'Setup 11:30–12:00 · SPM93 Partner Lunch', 'Requested 12:00–13:00 · SPM93 Partner Lunch' and 'Turnaround 13:00–13:45 · SPM93 Partner Lunch'. The 'Approved bookings' card lists SPM93 Morning Masterclass with '8 Jun 2027, 10:00–12:00' and 'Room in use 09:30–12:45'. The 'Requested, not yet approved' card lists SPM93 Partner Lunch with '10 Jun 2027, 12:00–13:00'. Nothing on the page mentions AM, PM or Night slots.</t>
@@ -12400,7 +12407,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC16</t>
         </is>
@@ -12412,7 +12419,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>`npm run fixtures:spm93` has been run since the last full `npx prisma db seed`, and no booking request has been sent for an 'SPM93 …' event since.
 SPM93 Studio is unavailable for maintenance on 16 Jun 2027, 14:00–18:00.
@@ -12427,7 +12434,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. On the 'SPM93 Studio' row, click 'View availability'
@@ -12442,7 +12449,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>SPM93 Studio: unavailable 16 Jun 2027, 14:00–18:00, reason Maintenance
 SPM93 Quick Room: setup 0 min, turnaround 0 min | Approved: SPM93 Quick Demo, 8 Jun 2027, 10:00–12:00</t>
@@ -12455,7 +12462,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: The 'Wed 16 Jun 2027' row lists 'Unavailable 14:00–18:00 · Maintenance' and nothing else; the rest of the day is not marked unavailable. The 'Unavailable periods' card lists 'Maintenance' with '16 Jun 2027, 14:00–18:00'.
 Step 4: The title changes to 'SPM93 Quick Room availability' and the subtitle ends 'setup 0 min, turnaround 0 min'. The 'Tue 8 Jun 2027' row lists only 'Booked 10:00–12:00 · SPM93 Quick Demo', with no 'Setup' or 'Turnaround' entry. The 'Approved bookings' card shows 'Room in use 10:00–12:00'.</t>
@@ -12468,7 +12475,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -12500,7 +12507,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: The 'Wed 16 Jun 2027' row lists 'Unavailable 14:00–18:00 · Maintenance' and nothing else; the rest of the day is not marked unavailable. The 'Unavailable periods' card lists 'Maintenance' with '16 Jun 2027, 14:00–18:00'.
 Step 4: The title changes to 'SPM93 Quick Room availability' and the subtitle ends 'setup 0 min, turnaround 0 min'. The 'Tue 8 Jun 2027' row lists only 'Booked 10:00–12:00 · SPM93 Quick Demo', with no 'Setup' or 'Turnaround' entry. The 'Approved bookings' card shows 'Room in use 10:00–12:00'.</t>
@@ -12568,7 +12575,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: The 'Wed 16 Jun 2027' row lists 'Unavailable 14:00–18:00 · Maintenance' and nothing else; the rest of the day is not marked unavailable. The 'Unavailable periods' card lists 'Maintenance' with '16 Jun 2027, 14:00–18:00'.
 Step 4: The title changes to 'SPM93 Quick Room availability' and the subtitle ends 'setup 0 min, turnaround 0 min'. The 'Tue 8 Jun 2027' row lists only 'Booked 10:00–12:00 · SPM93 Quick Demo', with no 'Setup' or 'Turnaround' entry. The 'Approved bookings' card shows 'Room in use 10:00–12:00'.</t>
@@ -13633,7 +13640,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC17</t>
         </is>
@@ -13645,7 +13652,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>`npm run fixtures:spm93` has been run since the last full `npx prisma db seed`.
 'SPM93 Morning Masterclass' holds an Approved booking at SPM93 Studio on 8 Jun 2027, 10:00–12:00 (room in use 09:30–12:45).
@@ -13660,7 +13667,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar and click 'Find a venue'
 2. Set 'From' to 8 Jun 2027, 08:15 and 'To' to 8 Jun 2027, 09:00, leave every other filter empty, and click 'Search'
@@ -13674,7 +13681,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>From: 8 Jun 2027, 08:15 | To: 8 Jun 2027, 09:00, then 08:45
 SPM93 Studio: setup 30 min, turnaround 45 min</t>
@@ -13687,7 +13694,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 2: 'SPM93 Studio' is not in the results (its turnaround would run to 09:45, into the Masterclass's setup from 09:30). 'SPM93 Quick Room' is in the results.
 Step 3: 'SPM93 Studio' is now in the results (the room would be in use 07:45–09:30, which only meets the Masterclass's setup).</t>
@@ -13700,7 +13707,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -13732,7 +13739,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 2: 'SPM93 Studio' is not in the results (its turnaround would run to 09:45, into the Masterclass's setup from 09:30). 'SPM93 Quick Room' is in the results.
 Step 3: 'SPM93 Studio' is now in the results (the room would be in use 07:45–09:30, which only meets the Masterclass's setup).</t>
@@ -13800,7 +13807,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 2: 'SPM93 Studio' is not in the results (its turnaround would run to 09:45, into the Masterclass's setup from 09:30). 'SPM93 Quick Room' is in the results.
 Step 3: 'SPM93 Studio' is now in the results (the room would be in use 07:45–09:30, which only meets the Masterclass's setup).</t>
@@ -14853,142 +14860,142 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Question / ambiguity for the PO or developer</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="2" ht="98.25" customHeight="1" s="19">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>Written before the code (TDD, 2026-10-08), then built to them on 2026-10-08: every label, message and page address in the cases is what the code shows (checked against the screens' automated tests, not yet walked through by hand). Checked against the Week 1 briefing, Week 4 instructions, Week 7 Customer Changes and the discussion logs up to 20261006 (#124-#129). Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
+      <c r="C2" s="23" t="n"/>
     </row>
     <row r="3" ht="111.75" customHeight="1" s="19">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-08: the request page (S-15, 'Request a venue booking') replaces the AM/PM/Night checkboxes with 'Date', 'Start time' and 'End time' fields (one date per request, as before). The time fields accept any minute, so an off-grid time reaches the page's own check and its message rather than the browser's. Under them: 'Setup: HH:MM–HH:MM (N min)', 'Turnaround: HH:MM–HH:MM (N min)' and 'Room in use: HH:MM–HH:MM', or 'No setup or turnaround needed at this venue.' and 'Room in use: …' when both are zero.</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="23" t="n"/>
     </row>
     <row r="4" ht="57.75" customHeight="1" s="19">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-08: refusal messages (AC3). Shown under the field: 'Choose a start time on a 15-minute step (:00, :15, :30 or :45).', 'Choose an end time on a 15-minute step (:00, :15, :30 or :45).', 'The end time must be after the start time.' The server applies the same checks.</t>
         </is>
       </c>
-      <c r="C4" s="18" t="n"/>
+      <c r="C4" s="23" t="n"/>
     </row>
     <row r="5" ht="57.75" customHeight="1" s="19">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-08: the SPM-42 rule that the request must cover the event's (or session's) own time is kept, reworded 'The requested times do not cover the event's time (&lt;date&gt;, &lt;times&gt;).' ('session's' for a session).</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="23" t="n"/>
     </row>
     <row r="6" ht="165.75" customHeight="1" s="19">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-08 (AC4, AC6): the whole room-in-use period, setup and turnaround included, must fit within the venue's opening hours, at request time and in Find a venue. Refusal: '&lt;venue&gt; is open 07:00–22:00. With its &lt;n&gt; min setup and &lt;n&gt; min turnaround, choose times between &lt;earliest start&gt; and &lt;latest end&gt;.' Not stated outright; inferred from Week 1 briefing (venue suitability depends on 'operating hours, setup requirements, and the turnaround time'), Week 7 Change #1 (setup and turnaround are when the venue is 'effectively occupied' and 'must be included when checking availability') and #46 (Venue Staff maintain operating hours). Our own question #131 (Q3, hours a venue can be booked) is still unanswered on 2026-10-08; if the customer rules otherwise, that ruling wins.</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n"/>
+      <c r="C6" s="23" t="n"/>
     </row>
     <row r="7" ht="165.75" customHeight="1" s="19">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-08: refusals follow SPM-44 (Detect Venue Booking Conflicts, merged to main 2026-10-08), which names what is in the way (its AC9), with SPM-93's times in place of slots. At request time: '&lt;venue&gt; is already booked for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.' and '&lt;venue&gt; is on hold for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;from&gt;–&lt;to&gt;.', where the times are the minutes both need; '&lt;venue&gt; is unavailable at this time (&lt;reason&gt;, &lt;the period's own times&gt;).'; a repeat of the same request: 'This event already has a pending request for &lt;venue&gt; on &lt;date&gt;, &lt;times&gt;.' At approval: 'This overlaps an approved booking: &lt;reference&gt; &lt;title&gt; holds &lt;venue&gt; on &lt;date&gt;, &lt;times&gt; (room in use &lt;times&gt;).' plus ' The clash is through setup or turnaround time.' when the event times themselves do not overlap.</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="23" t="n"/>
     </row>
     <row r="8" ht="98.25" customHeight="1" s="19">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-08: on Booking Requests (S-22) the 'Requested' row shows '&lt;date&gt;, &lt;start&gt;–&lt;end&gt;' with the Setup, Turnaround and Room in use lines underneath (AC8). The approve dialog reads 'This books &lt;venue&gt; for &lt;reference&gt; &lt;title&gt; on &lt;date&gt;, &lt;times&gt;. No other event can then be booked into the room from &lt;start&gt; to &lt;end&gt;, which includes its setup and turnaround time.' The event's Venue tab shows each request as '&lt;date&gt;, &lt;start&gt;–&lt;end&gt; · &lt;layout&gt;'.</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n"/>
+      <c r="C8" s="23" t="n"/>
     </row>
     <row r="9" ht="111.75" customHeight="1" s="19">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-08: venue form labels become 'Setup time (minutes)' and 'Turnaround time (minutes)' (the customer's word; the database field stays teardownMinutes). Hint 'In 15-minute steps: 0, 15, 30, 45 and so on.' Error 'Enter minutes in 15-minute steps: 0, 15, 30, 45 and so on.' The existing 'Enter a whole number of minutes, 0 or more.' still covers negative and non-numeric values. The calendar subtitle says 'turnaround' instead of 'teardown'. Week 7 Change #1 names only 'setup time' and 'turnaround time'; #43's 'teardown' is the same period.</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="23" t="n"/>
     </row>
     <row r="10" ht="125.25" customHeight="1" s="19">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-08 (AC9): the availability calendar (S-21) keeps one row per day but replaces the AM/PM/Night columns with one 'Schedule' column. Each entry reads '&lt;kind&gt; HH:MM–HH:MM · &lt;event title or reason&gt;', in time order, where kind is 'Setup', 'Booked', 'Turnaround', 'Requested' (a pending hold) or 'Unavailable'. An empty day shows 'Free' ('Closed' for a retired venue). The Unavailable periods card shows times, not just dates. The warning about minutes 'outside the AM, PM and Night slots' is removed. Layout is ours to choose: #6 says calendar granularity 'is a UI/UX question, please propose'.</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n"/>
+      <c r="C10" s="23" t="n"/>
     </row>
     <row r="11" ht="125.25" customHeight="1" s="19">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>OPEN for SPM-44's owner: SPM-44 (In Review) was merged to main with slot-based rules; this story moved its src/lib/venueConflict.ts to times, as SPM-93's description says it would. Two things change for SPM-44: (1) its test cases (docs/test-cases/SPM-44_test_cases.json) quote slot wording such as 'on 21 Oct 2026, AM' and will now read times; (2) SPM-44 had a pending request hold only its own slots, while SPM-93 (RESOLVED above, from #41 and Week 7 Change #1) has it hold its setup and turnaround too. SPM-44's acceptance criteria themselves are left as written.</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="23" t="n"/>
     </row>
     <row r="12" ht="84.75" customHeight="1" s="19">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Fixtures: scripts/seed-spm93.ts (`npm run fixtures:spm93`) deletes and recreates the 18 'SPM93 …' events (spm93_ seed keys) with their bookings and sessions, and resets SPM93 Studio (SPM93-STU), SPM93 Quick Room (SPM93-QCK) and SPM93 Settings Room (SPM93-SET) with Studio's one maintenance period. The same venues and events (without bookings, sessions or maintenance) are at the end of prisma/seed.ts.</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n"/>
+      <c r="C12" s="23" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="19"/>
     <row r="22" ht="15.75" customHeight="1" s="19"/>
@@ -16004,7 +16011,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC01</t>
         </is>
@@ -16016,7 +16023,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` from the project folder before this case (it only touches the 'SPM93 …' events and venues, never anyone else's data). Run it again after this case: the case sends a booking request.
 Logged out.</t>
@@ -16029,7 +16036,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Log in as daniel.tan@connectsphere.com / password123
 2. Click 'All Events' in the sidebar and open 'SPM93 Product Clinic'
@@ -16046,7 +16053,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM93 Product Clinic | When: 9 Jun 2027, 14:10–15:50 | No sessions | Status: Planning
 Venue: SPM93 Studio (SPM93-STU) | Open 07:00–22:00 | Setup 30 min | Turnaround 45 min</t>
@@ -16059,7 +16066,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: The 'Request a venue booking' page opens for 'SPM93 Product Clinic' at 'SPM93 Studio (SPM93-STU)'. There are no AM, PM or Night checkboxes. 'Date' shows 9 Jun 2027, 'Start time' shows 14:00 and 'End time' shows 16:00 (the event's 14:10–15:50 widened to the 15-minute grid). Below them: 'Setup: 13:30–14:00 (30 min)', 'Turnaround: 16:00–16:45 (45 min)' and 'Room in use: 13:30–16:45'.
 Step 5: A green alert 'Booking request sent to Venue Staff.' is shown.
@@ -16073,7 +16080,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -16105,7 +16112,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: The 'Request a venue booking' page opens for 'SPM93 Product Clinic' at 'SPM93 Studio (SPM93-STU)'. There are no AM, PM or Night checkboxes. 'Date' shows 9 Jun 2027, 'Start time' shows 14:00 and 'End time' shows 16:00 (the event's 14:10–15:50 widened to the 15-minute grid). Below them: 'Setup: 13:30–14:00 (30 min)', 'Turnaround: 16:00–16:45 (45 min)' and 'Room in use: 13:30–16:45'.
 Step 5: A green alert 'Booking request sent to Venue Staff.' is shown.
@@ -16174,7 +16181,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: The 'Request a venue booking' page opens for 'SPM93 Product Clinic' at 'SPM93 Studio (SPM93-STU)'. There are no AM, PM or Night checkboxes. 'Date' shows 9 Jun 2027, 'Start time' shows 14:00 and 'End time' shows 16:00 (the event's 14:10–15:50 widened to the 15-minute grid). Below them: 'Setup: 13:30–14:00 (30 min)', 'Turnaround: 16:00–16:45 (45 min)' and 'Room in use: 13:30–16:45'.
 Step 5: A green alert 'Booking request sent to Venue Staff.' is shown.
@@ -17240,7 +17247,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC02</t>
         </is>
@@ -17252,7 +17259,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>`npm run fixtures:spm93` has been run since the last full `npx prisma db seed`.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM93 …' event.
@@ -17266,7 +17273,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Two-Day Forum'
 2. Click the 'Venue' tab
@@ -17285,7 +17292,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM93 Two-Day Forum | Sessions: 'Day 1' 17 Jun 2027, 09:05–11:50; 'Day 2' 18 Jun 2027, 14:00–17:30
 Venue: SPM93 Studio (SPM93-STU) | Setup 30 min | Turnaround 45 min</t>
@@ -17298,7 +17305,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: The 'Request a venue booking' page shows 'Session: Day 1 — 17 Jun 2027, 09:05–11:50'. 'Date' shows 17 Jun 2027, 'Start time' 09:00 and 'End time' 12:00 (the session's times widened outwards to the grid, not the event's). 'Room in use: 08:30–12:45'.
 Step 5: The Venue tab opens again and no booking request has been added.
@@ -17313,7 +17320,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -17345,7 +17352,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: The 'Request a venue booking' page shows 'Session: Day 1 — 17 Jun 2027, 09:05–11:50'. 'Date' shows 17 Jun 2027, 'Start time' 09:00 and 'End time' 12:00 (the session's times widened outwards to the grid, not the event's). 'Room in use: 08:30–12:45'.
 Step 5: The Venue tab opens again and no booking request has been added.
@@ -17415,7 +17422,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: The 'Request a venue booking' page shows 'Session: Day 1 — 17 Jun 2027, 09:05–11:50'. 'Date' shows 17 Jun 2027, 'Start time' 09:00 and 'End time' 12:00 (the session's times widened outwards to the grid, not the event's). 'Room in use: 08:30–12:45'.
 Step 5: The Venue tab opens again and no booking request has been added.
@@ -18482,7 +18489,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC03</t>
         </is>
@@ -18494,7 +18501,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>`npm run fixtures:spm93` has been run since the last full `npx prisma db seed`.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -18508,7 +18515,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Validation Workshop'
 2. Click the 'Venue' tab
@@ -18527,7 +18534,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM93 Validation Workshop | When: 11 Jun 2027, 10:00–12:00
 Venue: SPM93 Studio (SPM93-STU)
@@ -18541,7 +18548,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: The request is not sent. Under 'Start time' the error 'Choose a start time on a 15-minute step (:00, :15, :30 or :45).' is shown. 'End time' has no error.
 Step 5: The request is not sent. The 'Start time' error is gone. Under 'End time' the error 'Choose an end time on a 15-minute step (:00, :15, :30 or :45).' is shown.
@@ -18557,7 +18564,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -18589,7 +18596,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: The request is not sent. Under 'Start time' the error 'Choose a start time on a 15-minute step (:00, :15, :30 or :45).' is shown. 'End time' has no error.
 Step 5: The request is not sent. The 'Start time' error is gone. Under 'End time' the error 'Choose an end time on a 15-minute step (:00, :15, :30 or :45).' is shown.
@@ -18660,7 +18667,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: The request is not sent. Under 'Start time' the error 'Choose a start time on a 15-minute step (:00, :15, :30 or :45).' is shown. 'End time' has no error.
 Step 5: The request is not sent. The 'Start time' error is gone. Under 'End time' the error 'Choose an end time on a 15-minute step (:00, :15, :30 or :45).' is shown.
@@ -19728,7 +19735,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC04</t>
         </is>
@@ -19740,7 +19747,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>`npm run fixtures:spm93` has been run since the last full `npx prisma db seed`.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).
@@ -19754,7 +19761,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Validation Workshop'
 2. Click the 'Venue' tab
@@ -19770,7 +19777,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM93 Validation Workshop | When: 11 Jun 2027, 10:00–12:00
 Requested: 11 Jun 2027, 10:30–12:00</t>
@@ -19783,7 +19790,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: The request is not sent. A red alert reads 'The requested times do not cover the event's time (11 Jun 2027, 10:00–12:00).'
 Step 5: The Venue tab opens and its 'Booking requests' card has no request for SPM93 Studio.</t>
@@ -19796,7 +19803,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -19828,7 +19835,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: The request is not sent. A red alert reads 'The requested times do not cover the event's time (11 Jun 2027, 10:00–12:00).'
 Step 5: The Venue tab opens and its 'Booking requests' card has no request for SPM93 Studio.</t>
@@ -19896,7 +19903,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: The request is not sent. A red alert reads 'The requested times do not cover the event's time (11 Jun 2027, 10:00–12:00).'
 Step 5: The Venue tab opens and its 'Booking requests' card has no request for SPM93 Studio.</t>
@@ -20961,7 +20968,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC05</t>
         </is>
@@ -20973,7 +20980,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` before this case, and again after it: the case sends two booking requests.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
@@ -20986,7 +20993,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Lunch and Learn'
 2. Click the 'Venue' tab
@@ -21006,7 +21013,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Events: SPM93 Lunch and Learn, 14 Jun 2027, 12:00–13:00; SPM93 Sunset Talk, 14 Jun 2027, 18:00–19:00
 Venue: SPM93 Quick Room (SPM93-QCK) | Open 07:00–22:00 | Setup 0 min | Turnaround 0 min</t>
@@ -21019,7 +21026,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Date' shows 14 Jun 2027, 'Start time' 12:00 and 'End time' 13:00.
 Step 4: A green alert 'Booking request sent to Venue Staff.' is shown.
@@ -21035,7 +21042,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -21067,7 +21074,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Date' shows 14 Jun 2027, 'Start time' 12:00 and 'End time' 13:00.
 Step 4: A green alert 'Booking request sent to Venue Staff.' is shown.
@@ -21138,7 +21145,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 3: 'Date' shows 14 Jun 2027, 'Start time' 12:00 and 'End time' 13:00.
 Step 4: A green alert 'Booking request sent to Venue Staff.' is shown.
@@ -22206,7 +22213,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC06</t>
         </is>
@@ -22218,7 +22225,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` before this case, and again after it: the case sends two booking requests.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
@@ -22231,7 +22238,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM93 Breakfast Briefing'
 2. Click the 'Venue' tab
@@ -22252,7 +22259,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Venue: SPM93 Studio (SPM93-STU) | Open 07:00–22:00 | Setup 30 min | Turnaround 45 min
 Events: SPM93 Breakfast Briefing, 13 Jun 2027, 07:30–09:00; SPM93 Evening Forum, 13 Jun 2027, 20:00–21:15
@@ -22266,7 +22273,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Room in use: 06:45–09:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is open 07:00–22:00. With its 30 min setup and 45 min turnaround, choose times between 07:30 and 21:15.'
 Step 5: A green alert 'Booking request sent to Venue Staff.' is shown: setup starts exactly at opening time.
@@ -22281,7 +22288,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -22313,7 +22320,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Room in use: 06:45–09:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is open 07:00–22:00. With its 30 min setup and 45 min turnaround, choose times between 07:30 and 21:15.'
 Step 5: A green alert 'Booking request sent to Venue Staff.' is shown: setup starts exactly at opening time.
@@ -22383,7 +22390,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 4: 'Room in use: 06:45–09:45' is shown. The request is not sent; a red alert reads 'SPM93 Studio is open 07:00–22:00. With its 30 min setup and 45 min turnaround, choose times between 07:30 and 21:15.'
 Step 5: A green alert 'Booking request sent to Venue Staff.' is shown: setup starts exactly at opening time.
@@ -23428,7 +23435,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="19" min="1" max="1"/>
@@ -23436,46 +23443,53 @@
     <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="19">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="19">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): After a save that flags no booking, the venue page now reads 'No bookings were affected, so nobody needed to be notified.' instead of 'No approved bookings were affected, so nobody needed to be notified.' (SPM-80, Week 7 Change #1: changing a venue's setup or turnaround time now re-checks pending requests as well as approved bookings). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="19">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="19">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" s="19">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>SPM-93-TC07</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="57.75" customHeight="1" s="19">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="4" ht="57.75" customHeight="1" s="19">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm93` before this case, and again after it: the case changes SPM93 Settings Room, a venue with no bookings that only this case uses.
 Logged out.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="125.25" customHeight="1" s="19">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5" ht="125.25" customHeight="1" s="19">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Venues' in the sidebar and click the 'SPM93 Settings Room' row
@@ -23485,13 +23499,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="57.75" customHeight="1" s="19">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="57.75" customHeight="1" s="19">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Venue: SPM93 Settings Room (SPM93-SET) | Before: setup 30 min, turnaround 45 min
 Refused: setup 20, turnaround 50
@@ -23499,13 +23513,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="165.75" customHeight="1" s="19">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="165.75" customHeight="1" s="19">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 2: The venue edit page opens with 'Setup time (minutes)' 30 and 'Turnaround time (minutes)' 45. The hint under the setup field reads 'In 15-minute steps: 0, 15, 30, 45 and so on.'
 Step 3: Nothing is saved. Under 'Setup time (minutes)' and under 'Turnaround time (minutes)' the error 'Enter minutes in 15-minute steps: 0, 15, 30, 45 and so on.' is shown.
@@ -23514,45 +23528,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="19">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="19">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="19">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1" s="19">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B9" s="16" t="n">
         <v>46303</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="19"/>
-    <row r="10" ht="15.75" customHeight="1" s="19">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="19"/>
+    <row r="11" ht="15.75" customHeight="1" s="19">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="19">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="19">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 2: The venue edit page opens with 'Setup time (minutes)' 30 and 'Turnaround time (minutes)' 45. The hint under the setup field reads 'In 15-minute steps: 0, 15, 30, 45 and so on.'
 Step 3: Nothing is saved. Under 'Setup time (minutes)' and under 'Turnaround time (minutes)' the error 'Enter minutes in 15-minute steps: 0, 15, 30, 45 and so on.' is shown.
@@ -23561,68 +23575,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="19">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="19">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="19">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Kayal</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="19">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Kayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="19">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>46304</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="19"/>
-    <row r="17" ht="15.75" customHeight="1" s="19">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="19"/>
+    <row r="18" ht="15.75" customHeight="1" s="19">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="19">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="19">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 2: The venue edit page opens with 'Setup time (minutes)' 30 and 'Turnaround time (minutes)' 45. The hint under the setup field reads 'In 15-minute steps: 0, 15, 30, 45 and so on.'
 Step 3: Nothing is saved. Under 'Setup time (minutes)' and under 'Turnaround time (minutes)' the error 'Enter minutes in 15-minute steps: 0, 15, 30, 45 and so on.' is shown.
@@ -23631,53 +23645,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="19">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="19">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="19">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="19">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B23" s="16" t="n">
         <v>46304</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="19"/>
     <row r="24" ht="15.75" customHeight="1" s="19"/>
     <row r="25" ht="15.75" customHeight="1" s="19"/>
     <row r="26" ht="15.75" customHeight="1" s="19"/>
@@ -24656,6 +24669,9 @@
     <row r="999" ht="15.75" customHeight="1" s="19"/>
     <row r="1000" ht="15.75" customHeight="1" s="19"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/docs/test-cases/SPM-93_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-93_Test_Cases.xlsx
@@ -499,7 +499,6 @@
       <c r="E1" s="20" t="n"/>
       <c r="F1" s="21" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="22" t="inlineStr">
         <is>
@@ -23446,7 +23445,7 @@
     <row r="1" ht="90" customHeight="1" s="19">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>v2 (2026-10-20): After a save that flags no booking, the venue page now reads 'No bookings were affected, so nobody needed to be notified.' instead of 'No approved bookings were affected, so nobody needed to be notified.' (SPM-80, Week 7 Change #1: changing a venue's setup or turnaround time now re-checks pending requests as well as approved bookings). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+          <t>v2 (2026-10-20): After a save that flags no booking, the venue page now reads 'No bookings were affected, so nobody needed to be notified.' instead of 'No approved bookings were affected, so nobody needed to be notified.' (SPM-80, Week 7 Change #1: changing a venue's setup or turnaround time now re-checks pending requests as well as approved bookings). Also, on the venue edit page the hint under 'Setup time (minutes)' now reads 'In 15-minute steps: 0, 15, 30, 45 and so on. Changing it re-checks this venue's upcoming bookings.', and 'Turnaround time (minutes)' has the hint 'Changing the setup or turnaround time re-checks this venue's upcoming bookings. Any that now clash are flagged for their coordinator, never changed.' Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
         </is>
       </c>
     </row>
